--- a/financial_advisor_forms/027_fuel_cost_calculator--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/027_fuel_cost_calculator--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_5}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 5}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_3}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 3}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_1}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 1}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'gallons',_'value':_'gallons'}</t>
+          <t>gallons</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Gallons', 'value': 'Gallons'}</t>
+          <t>Gallons</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'kiloliters',_'value':_'kiloliters'}</t>
+          <t>kiloliters</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Kiloliters', 'value': 'Kiloliters'}</t>
+          <t>Kiloliters</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'liters',_'value':_'liters'}</t>
+          <t>liters</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Liters', 'value': 'Liters'}</t>
+          <t>Liters</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'ounces',_'value':_'ounces'}</t>
+          <t>ounces</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Ounces', 'value': 'Ounces'}</t>
+          <t>Ounces</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'tonnes',_'value':_'tonnes'}</t>
+          <t>tonnes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Tonnes', 'value': 'Tonnes'}</t>
+          <t>Tonnes</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'diesel',_'value':_'diesel'}</t>
+          <t>diesel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Diesel', 'value': 'diesel'}</t>
+          <t>Diesel</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'electric',_'value':_'electric'}</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Electric', 'value': 'electric'}</t>
+          <t>Electric</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'gasoline',_'value':_'gasoline'}</t>
+          <t>gasoline</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Gasoline', 'value': 'gasoline'}</t>
+          <t>Gasoline</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'directly_injected',_'value':_'direct_injected'}</t>
+          <t>directly_injected</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Directly Injected', 'value': 'direct_injected'}</t>
+          <t>Directly Injected</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'indirectly_injected',_'value':_'indirectly_injected'}</t>
+          <t>indirectly_injected</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Indirectly Injected', 'value': 'indirectly_injected'}</t>
+          <t>Indirectly Injected</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'diesel',_'value':_'diesel'}</t>
+          <t>diesel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Diesel', 'value': 'diesel'}</t>
+          <t>Diesel</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'electric',_'value':_'electric'}</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Electric', 'value': 'electric'}</t>
+          <t>Electric</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'gasoline',_'value':_'gasoline'}</t>
+          <t>gasoline</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Gasoline', 'value': 'gasoline'}</t>
+          <t>Gasoline</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 'low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 'medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 'high'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
